--- a/out/MLP-S4_repeat_5_000006.xlsx
+++ b/out/MLP-S4_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>3.171991106271274</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.171991106271274</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.171991106271274</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.171991106271274</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.171991106271274</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.171991106271274</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.571991106271275</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.571991106271275</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.171991106271274</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.171991106271274</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.171991106271274</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.171991106271274</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004499999204052146</v>
+        <v>-0.0003157362883755704</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5791847404061293</v>
+        <v>0.4063771978125408</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.171991106271274</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.159465998829599</v>
+        <v>0.8135234567621262</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.133757660132265</v>
+        <v>-0.09384919839045652</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.171991106271274</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3122122631337086</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.171991106271274</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3122122631337086</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>3.171991106271274</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4444463215351319</v>
+        <v>0.3119395593627775</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.630605876750714</v>
+        <v>0.8378049617599905</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.708904992455305</v>
+        <v>1.989217748380041</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.3119979993172539</v>
+        <v>0.1603044772398999</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.571991106271275</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.69991568854322</v>
+        <v>1.470799253085561</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.5464943026350069</v>
+        <v>0.280788494856039</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.571991106271275</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.481059109383318</v>
+        <v>1.872150656926576</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.299279929114159</v>
+        <v>0.1537699978437589</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>3.171991106271274</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.532654096869145</v>
+        <v>1.898660176554134</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1236069692237599</v>
+        <v>0.06350944531748137</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.480274284519346</v>
+        <v>1.871747393430854</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1540036764173866</v>
+        <v>0.07912731885218854</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.571991106271275</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.664696003106345</v>
+        <v>1.966503245593791</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.09273010622257385</v>
+        <v>0.04764427641955696</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.696048233012043</v>
+        <v>1.982611965998917</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0704998092015519</v>
+        <v>0.0362224582064275</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.571991106271275</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.744278736258701</v>
+        <v>2.007392862784966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.03118304347143281</v>
+        <v>0.01602128753074481</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.736081036857177</v>
+        <v>2.003180824539951</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.02474271910621464</v>
+        <v>0.01271199196242541</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.754374724556642</v>
+        <v>2.012579705318727</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01226976365203787</v>
+        <v>0.006301231743792023</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.571991106271275</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.754150650490029</v>
+        <v>2.012462133976996</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.007131269429029264</v>
+        <v>0.003663502140238851</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>3.171991106271274</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.756139853465354</v>
+        <v>2.013482072908368</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003564589314887446</v>
+        <v>0.001827796469746611</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.756130409085691</v>
+        <v>2.013474790953039</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001757159323539984</v>
+        <v>0.0009005141711502362</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.75608076719836</v>
+        <v>2.013446834177265</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.00101965940281614</v>
+        <v>0.0005223491389086324</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.756359123552132</v>
+        <v>2.013587665786047</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0003364914274377019</v>
+        <v>0.0001713256390037807</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.756013841451205</v>
+        <v>2.01340753616449</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001679259183398704</v>
+        <v>8.258585474357068e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.756010754914571</v>
+        <v>2.013403519158898</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>8.795545294412324e-05</v>
+        <v>4.392392260217012e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.756021088134544</v>
+        <v>2.013406483671643</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>4.003342849230196e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.756013063444647</v>
+        <v>2.013399931785913</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>2.409200745629541e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.756018820581137</v>
+        <v>2.013400310354159</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>7.887479732251461e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.756010483429768</v>
+        <v>2.013393643390288</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.756007378744518</v>
+        <v>2.013389781315192</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.756003059753369</v>
+        <v>2.013385234003007</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.75599823558048</v>
+        <v>2.013385323947657</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.755997377646895</v>
+        <v>2.013384466014072</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.755997605967929</v>
+        <v>2.013384694335107</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.755996810303718</v>
+        <v>2.013383898670895</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.755996872573091</v>
+        <v>2.013383960940268</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.755996900248368</v>
+        <v>2.013383988615545</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.755997052462391</v>
+        <v>2.013384140829568</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.755996706521429</v>
+        <v>2.013383794888606</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.75599678262844</v>
+        <v>2.013383870995618</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.755996948680102</v>
+        <v>2.01338403704728</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.755997308458703</v>
+        <v>2.01338439682588</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.75599732921516</v>
+        <v>2.013384417582337</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.755997432997448</v>
+        <v>2.013384521364626</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.755997661318483</v>
+        <v>2.013384749685661</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.755997536779737</v>
+        <v>2.013384625146914</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.755997564455014</v>
+        <v>2.013384652822191</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.755997619805568</v>
+        <v>2.013384708172745</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.755997882720699</v>
+        <v>2.013384971087876</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.755997799694868</v>
+        <v>2.013384888062045</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.755997592130291</v>
+        <v>2.013384680497468</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.755997605967929</v>
+        <v>2.013384694335107</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.755997744344314</v>
+        <v>2.013384832711491</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.755997460672726</v>
+        <v>2.013384549039903</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.755997287702245</v>
+        <v>2.013384376069422</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.755997183919956</v>
+        <v>2.013384272287134</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.75599732921516</v>
+        <v>2.013384417582337</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.755997571373833</v>
+        <v>2.013384659741011</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.755997398403352</v>
+        <v>2.01338448677053</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.755997100894125</v>
+        <v>2.013384189261303</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.755997087056487</v>
+        <v>2.013384175423664</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.755996720359068</v>
+        <v>2.013383808726245</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.755996720359068</v>
+        <v>2.013383808726245</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.755996658089694</v>
+        <v>2.013383746456872</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.755996554307406</v>
+        <v>2.013383642674583</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.755996381336926</v>
+        <v>2.013383469704102</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.75599642976866</v>
+        <v>2.013383518135837</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.755996069990059</v>
+        <v>2.013383158357237</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.755996028477144</v>
+        <v>2.013383116844321</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.755996083827699</v>
+        <v>2.013383172194875</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.755996139178252</v>
+        <v>2.013383227545429</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.755996180691168</v>
+        <v>2.013383269058345</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.755995910857217</v>
+        <v>2.013382999224394</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.755995966207772</v>
+        <v>2.013383054574948</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.755996111502975</v>
+        <v>2.013383199870153</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.755996076908879</v>
+        <v>2.013383165276056</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.755996063071241</v>
+        <v>2.013383151438418</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.75599615301589</v>
+        <v>2.013383241383068</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>3.171991106271274</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.755996471281575</v>
+        <v>2.013383559648752</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.755996291392275</v>
+        <v>2.013383379759452</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.755996332905191</v>
+        <v>2.013383421272368</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.755996146097071</v>
+        <v>2.013383234464249</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.755996215285264</v>
+        <v>2.013383303652441</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.755996014639506</v>
+        <v>2.013383103006683</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.755996056152421</v>
+        <v>2.013383144519599</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.755996083827699</v>
+        <v>2.013383172194875</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_5_000006.xlsx
+++ b/out/MLP-S4_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>3.171991106271274</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-0.3079679992113873</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.3079679992113873</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.3044764438639379</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.171991106271274</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3824533321832731</v>
+        <v>1.316920886939263</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.171991106271274</v>
+        <v>1.316920886939263</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.171991106271274</v>
+        <v>1.316920886939263</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3824533321832731</v>
+        <v>1.316920886939263</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.171991106271274</v>
+        <v>0.5044764438639379</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.3044764438639379</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.3044764438639379</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.571991106271275</v>
+        <v>0.3044764438639378</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.3044764438639379</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.3044764438639379</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.571991106271275</v>
+        <v>0.3044764438639379</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.171991106271274</v>
+        <v>1.316920886939263</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004499999204052146</v>
+        <v>-0.0003444280517701991</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5791847404061293</v>
+        <v>0.4433057322823057</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.159465998829599</v>
+        <v>0.8874504122525295</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.133757660132265</v>
+        <v>-0.1023775148815813</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3405837893489541</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3405837893489541</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>3.171991106271274</v>
+        <v>1.316920886939263</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4444463215351319</v>
+        <v>0.3403009519183221</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.630605876750714</v>
+        <v>0.8689375936911733</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.116920886939263</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.708904992455305</v>
+        <v>2.079906722329196</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.3119979993172539</v>
+        <v>0.1662614176649596</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.571991106271275</v>
+        <v>1.116920886939263</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.69991568854322</v>
+        <v>1.542223718958239</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.5464943026350069</v>
+        <v>0.2912228584920443</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.571991106271275</v>
+        <v>1.929365330014588</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.481059109383318</v>
+        <v>1.958489394213121</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.299279929114159</v>
+        <v>0.1594839968215566</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>3.171991106271274</v>
+        <v>1.116920886939263</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.532654096869145</v>
+        <v>1.985983989817613</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1236069692237599</v>
+        <v>0.06586921329857975</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.116920886939263</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.480274284519346</v>
+        <v>1.958071147624323</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1540036764173866</v>
+        <v>0.08206787767507677</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.571991106271275</v>
+        <v>0.304476443863938</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.664696003106345</v>
+        <v>2.056348351971813</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.09273010622257385</v>
+        <v>0.04941487266987717</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.116920886939263</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.696048233012043</v>
+        <v>2.073055710593899</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0704998092015519</v>
+        <v>0.03756948536106954</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.571991106271275</v>
+        <v>0.304476443863938</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.744278736258701</v>
+        <v>2.098757511376871</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.03118304347143281</v>
+        <v>0.01661708114677311</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.304476443863938</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.736081036857177</v>
+        <v>2.094389052720911</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.02474271910621464</v>
+        <v>0.01318364557150386</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.304476443863938</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.754374724556642</v>
+        <v>2.104136674285098</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01226976365203787</v>
+        <v>0.006536370888542697</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.571991106271275</v>
+        <v>1.116920886939264</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.754150650490029</v>
+        <v>2.10401492704968</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.007131269429029264</v>
+        <v>0.00379732537453781</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>3.171991106271274</v>
+        <v>1.116920886939264</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.756139853465354</v>
+        <v>2.10507266292322</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003564589314887446</v>
+        <v>0.00189761728764172</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.756130409085691</v>
+        <v>2.10506529403626</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001757159323539984</v>
+        <v>0.0009350099490988166</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.75608076719836</v>
+        <v>2.105036498628613</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.00101965940281614</v>
+        <v>0.0005390374027981461</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.756359123552132</v>
+        <v>2.105182408722612</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0003364914274377019</v>
+        <v>0.0001780215493456964</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.756013841451205</v>
+        <v>2.104995628609097</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001679259183398704</v>
+        <v>8.707743703811276e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.756010754914571</v>
+        <v>2.104991647466214</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>8.795545294412324e-05</v>
+        <v>4.392392260217012e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.756021088134544</v>
+        <v>2.104994812624717</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>4.003342849230196e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.756013063444647</v>
+        <v>2.104988184631976</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>2.409200745629541e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.756018820581137</v>
+        <v>2.104989102868121</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>7.887479732251461e-06</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.756010483429768</v>
+        <v>2.1049821005773</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.756007378744518</v>
+        <v>2.104978238502204</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.756003059753369</v>
+        <v>2.104973691190019</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.75599823558048</v>
+        <v>2.104973781134669</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.755997377646895</v>
+        <v>2.104972923201084</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.755997605967929</v>
+        <v>2.104973151522119</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.755996810303718</v>
+        <v>2.104972355857907</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.755996872573091</v>
+        <v>2.10497241812728</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.755996900248368</v>
+        <v>2.104972445802557</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.755997052462391</v>
+        <v>2.10497259801658</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.755996706521429</v>
+        <v>2.104972252075619</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.75599678262844</v>
+        <v>2.10497232818263</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.755996948680102</v>
+        <v>2.104972494234292</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.755997308458703</v>
+        <v>2.104972854012892</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.75599732921516</v>
+        <v>2.104972874769349</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.755997432997448</v>
+        <v>2.104972978551638</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.755997661318483</v>
+        <v>2.104973206872673</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.755997536779737</v>
+        <v>2.104973082333927</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.755997564455014</v>
+        <v>2.104973110009204</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.755997619805568</v>
+        <v>2.104973165359757</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.755997882720699</v>
+        <v>2.104973428274888</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.755997799694868</v>
+        <v>2.104973345249057</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.755997592130291</v>
+        <v>2.10497313768448</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.755997605967929</v>
+        <v>2.104973151522119</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.755997744344314</v>
+        <v>2.104973289898504</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.755997460672726</v>
+        <v>2.104973006226915</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.755997287702245</v>
+        <v>2.104972833256434</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.755997183919956</v>
+        <v>2.104972729474146</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.75599732921516</v>
+        <v>2.104972874769349</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.755997571373833</v>
+        <v>2.104973116928023</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.755997398403352</v>
+        <v>2.104972943957542</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.755997100894125</v>
+        <v>2.104972646448315</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.755997087056487</v>
+        <v>2.104972632610676</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.755996720359068</v>
+        <v>2.104972265913257</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.755996720359068</v>
+        <v>2.104972265913257</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.755996658089694</v>
+        <v>2.104972203643884</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.755996554307406</v>
+        <v>2.104972099861596</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.755996381336926</v>
+        <v>2.104971926891114</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.75599642976866</v>
+        <v>2.104971975322849</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.755996069990059</v>
+        <v>2.104971615544249</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.755996028477144</v>
+        <v>2.104971574031334</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.755996083827699</v>
+        <v>2.104971629381887</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.755996139178252</v>
+        <v>2.104971684732442</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.755996180691168</v>
+        <v>2.104971726245357</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.755995910857217</v>
+        <v>2.104971456411407</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.755995966207772</v>
+        <v>2.104971511761961</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.755996111502975</v>
+        <v>2.104971657057165</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.755996076908879</v>
+        <v>2.104971622463069</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.755996063071241</v>
+        <v>2.10497160862543</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.75599615301589</v>
+        <v>2.10497169857008</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>3.171991106271274</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.755996471281575</v>
+        <v>2.104972016835764</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.755996291392275</v>
+        <v>2.104971836946465</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-0.3079679992113873</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.755996332905191</v>
+        <v>2.10497187845938</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.3079679992113873</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.755996146097071</v>
+        <v>2.104971691651261</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.755996215285264</v>
+        <v>2.104971760839453</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.755996014639506</v>
+        <v>2.104971560193696</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.755996056152421</v>
+        <v>2.104971601706611</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.755996083827699</v>
+        <v>2.104971629381887</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_5_000006.xlsx
+++ b/out/MLP-S4_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3967665433883667</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4057578146457672</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4312838017940521</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4689062535762787</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4189232587814331</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4571245610713959</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4090531170368195</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.479686439037323</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4870549738407135</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4426199793815613</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4184735119342804</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3971226811408997</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4602030515670776</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4195317924022675</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4130118787288666</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4121556580066681</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4503567516803741</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4828585982322693</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.504476443863938</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5337554216384888</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.504476443863938</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4767839312553406</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.504476443863938</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4586305618286133</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3079679992113873</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4312834143638611</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3079679992113873</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4406760036945343</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3044764438639379</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5203529596328735</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.504476443863938</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4543633162975311</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.316920886939263</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5487743020057678</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.316920886939263</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.6634764075279236</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.129365330014588</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5658758282661438</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.316920886939263</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4945375919342041</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.316920886939263</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.508108913898468</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5044764438639379</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4449192881584167</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3044764438639379</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4100190997123718</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4463480412960052</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3044764438639379</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5741239786148071</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3044764438639378</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4980754852294922</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3044764438639379</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4945715367794037</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3044764438639379</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5317423939704895</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.3044764438639379</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4655180275440216</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.504476443863938</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4851484000682831</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.504476443863938</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5318329334259033</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.316920886939263</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5817013382911682</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.129365330014588</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5949527025222778</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.129365330014588</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6845176219940186</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.129365330014588</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003444280517701991</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4433057322823057</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6479754447937012</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.129365330014588</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8874504122525295</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1023775148815813</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5057786107063293</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.129365330014588</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3405837893489541</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5461944341659546</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.129365330014588</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3405837893489541</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5342255830764771</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.316920886939263</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3403009519183221</v>
+        <v>0.1805492523242068</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8689375936911733</v>
+        <v>0.1854226701566546</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4615491628646851</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.116920886939263</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.079906722329196</v>
+        <v>0.5517641376967581</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1662614176649596</v>
+        <v>0.0354786007527919</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5566086769104004</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.116920886939263</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.542223718958239</v>
+        <v>0.4370277559345695</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2912228584920443</v>
+        <v>0.06214413394122734</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.532653272151947</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.929365330014588</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.958489394213121</v>
+        <v>0.5258548144014841</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1594839968215566</v>
+        <v>0.03403238920826912</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.5305706262588501</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.116920886939263</v>
+        <v>-0.16</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.985983989817613</v>
+        <v>0.5317218943881942</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06586921329857975</v>
+        <v>0.01405587236647913</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4859151542186737</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.116920886939263</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.958071147624323</v>
+        <v>0.5257655733604077</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.08206787767507677</v>
+        <v>0.01751192035485199</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.646406352519989</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.304476443863938</v>
+        <v>0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.056348351971813</v>
+        <v>0.5467368825751256</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04941487266987717</v>
+        <v>0.01054288952356224</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4966158270835876</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.116920886939263</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.073055710593899</v>
+        <v>0.5503006069246938</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03756948536106954</v>
+        <v>0.008015056170379379</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.7070913910865784</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.304476443863938</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.098757511376871</v>
+        <v>0.5557830431526014</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01661708114677311</v>
+        <v>0.003542299890334637</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3956181406974792</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.304476443863938</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.094389052720911</v>
+        <v>0.5548469297300284</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01318364557150386</v>
+        <v>0.002809788383591186</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3008256256580353</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.304476443863938</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.104136674285098</v>
+        <v>0.5569231848985744</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006536370888542697</v>
+        <v>0.001390825986924216</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.7938657402992249</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.116920886939264</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.10401492704968</v>
+        <v>0.5568932728689899</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.00379732537453781</v>
+        <v>0.0008066670080306419</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7441325783729553</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.116920886939264</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.10507266292322</v>
+        <v>0.5571150436555501</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.00189761728764172</v>
+        <v>0.0003993789036425062</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.439499169588089</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.504476443863938</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.10506529403626</v>
+        <v>0.5571095401765174</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009350099490988166</v>
+        <v>0.0001962253713667192</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4445913434028625</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.105036498628613</v>
+        <v>0.5570994463583666</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005390374027981461</v>
+        <v>0.0001118178472265958</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.454659104347229</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.105182408722612</v>
+        <v>0.5571267508286664</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001780215493456964</v>
+        <v>3.294349193752244e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.2539568245410919</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.104995628609097</v>
+        <v>0.5570829576964944</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.707743703811276e-05</v>
+        <v>1.521212032543939e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.2804724872112274</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.104991647466214</v>
+        <v>0.5570781813480568</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.392392260217012e-05</v>
+        <v>4.784784520434025e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.2517865896224976</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.104994812624717</v>
+        <v>0.5570749748963635</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.2982690930366516</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.104988184631976</v>
+        <v>0.5570695884122059</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3553540408611298</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.104989102868121</v>
+        <v>0.557066203793755</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3431870341300964</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.1049821005773</v>
+        <v>0.5570605363634813</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3794097304344177</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.104978238502204</v>
+        <v>0.5570609168985391</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.2934730648994446</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.104973691190019</v>
+        <v>0.5570611452195737</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3313387632369995</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.104973781134669</v>
+        <v>0.5570612351642237</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2854584157466888</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.104972923201084</v>
+        <v>0.5570603772306388</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.2889596819877625</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.104973151522119</v>
+        <v>0.5570606055516736</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.2842498421669006</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.104972355857907</v>
+        <v>0.5570598098874618</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.2346344590187073</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.10497241812728</v>
+        <v>0.5570598721568349</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2528998553752899</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.104972445802557</v>
+        <v>0.5570598998321118</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.2871746122837067</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.10497259801658</v>
+        <v>0.5570600520461351</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2486260235309601</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.104972252075619</v>
+        <v>0.5570597061051733</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.2673453986644745</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.10497232818263</v>
+        <v>0.557059782212185</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.262355238199234</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.104972494234292</v>
+        <v>0.5570599482638465</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3852280080318451</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.104972854012892</v>
+        <v>0.5570603080424467</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4167646169662476</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.104972874769349</v>
+        <v>0.5570603287989043</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4814322292804718</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.104972978551638</v>
+        <v>0.5570604325811929</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3932409584522247</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.104973206872673</v>
+        <v>0.5570606609022275</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3640533685684204</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.104973082333927</v>
+        <v>0.5570605363634813</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3260749578475952</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.104973110009204</v>
+        <v>0.5570605640387581</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.4622873067855835</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.104973165359757</v>
+        <v>0.5570606193893121</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3475544154644012</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.104973428274888</v>
+        <v>0.5570608823044428</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.3457597196102142</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.104973345249057</v>
+        <v>0.557060799278612</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3509490787982941</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.10497313768448</v>
+        <v>0.5570605917140352</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3343164026737213</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.104973151522119</v>
+        <v>0.5570606055516736</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3478979170322418</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.104973289898504</v>
+        <v>0.5570607439280583</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3758060038089752</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.104973006226915</v>
+        <v>0.5570604602564697</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.353064626455307</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.104972833256434</v>
+        <v>0.5570602872859889</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4450938403606415</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.104972729474146</v>
+        <v>0.5570601835037005</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4208905398845673</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.104972874769349</v>
+        <v>0.5570603287989043</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3770842850208282</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.104973116928023</v>
+        <v>0.5570605709575775</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3685189187526703</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.104972943957542</v>
+        <v>0.5570603979870966</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3306503593921661</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.104972646448315</v>
+        <v>0.5570601004778696</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.353323221206665</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.104972632610676</v>
+        <v>0.5570600866402311</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3545763194561005</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.104972265913257</v>
+        <v>0.5570597199428119</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3840214014053345</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.104972265913257</v>
+        <v>0.5570597199428119</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4258686006069183</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.104972203643884</v>
+        <v>0.5570596576734388</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3438873887062073</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.104972099861596</v>
+        <v>0.5570595538911502</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3449608087539673</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.104971926891114</v>
+        <v>0.5570593809206695</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3609604835510254</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.104971975322849</v>
+        <v>0.557059429352404</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3394591510295868</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.104971615544249</v>
+        <v>0.557059069573804</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3290132582187653</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.104971574031334</v>
+        <v>0.5570590280608886</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3943668603897095</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.104971629381887</v>
+        <v>0.5570590834114424</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3399249017238617</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.104971684732442</v>
+        <v>0.5570591387619963</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3507423400878906</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.104971726245357</v>
+        <v>0.5570591802749116</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3606286346912384</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.104971456411407</v>
+        <v>0.5570589104409616</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.376466691493988</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.104971511761961</v>
+        <v>0.5570589657915156</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3680460453033447</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.104971657057165</v>
+        <v>0.5570591110867195</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3776938319206238</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.104971622463069</v>
+        <v>0.5570590764926232</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.35674187541008</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.10497160862543</v>
+        <v>0.5570590626549846</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4404976069927216</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.504476443863938</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.10497169857008</v>
+        <v>0.5570591525996348</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.5457426309585571</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.504476443863938</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.104972016835764</v>
+        <v>0.5570594708653195</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4174843430519104</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.504476443863938</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.104971836946465</v>
+        <v>0.5570592909760194</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3805781304836273</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3079679992113873</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.10497187845938</v>
+        <v>0.5570593324889347</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3810614049434662</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3079679992113873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.104971691651261</v>
+        <v>0.5570591456808155</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3234411478042603</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.104971760839453</v>
+        <v>0.5570592148690079</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3378573954105377</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.104971560193696</v>
+        <v>0.5570590142232501</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3077752590179443</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-1</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.104971601706611</v>
+        <v>0.5570590557361655</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.3310103416442871</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.104971629381887</v>
+        <v>0.5570590834114424</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_5_000006.xlsx
+++ b/out/MLP-S4_repeat_5_000006.xlsx
@@ -67724,7 +67724,7 @@
         <v>0.4814322292804718</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0.5570604325811929</v>
@@ -68519,7 +68519,7 @@
         <v>0.3932409584522247</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0.5570606609022275</v>
@@ -69314,7 +69314,7 @@
         <v>0.3640533685684204</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0.5570605363634813</v>
@@ -70109,7 +70109,7 @@
         <v>0.3260749578475952</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0.5570605640387581</v>
@@ -70904,7 +70904,7 @@
         <v>0.4622873067855835</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC88" t="n">
         <v>0.5570606193893121</v>
@@ -71699,7 +71699,7 @@
         <v>0.3475544154644012</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
         <v>0.5570608823044428</v>
@@ -74084,7 +74084,7 @@
         <v>0.3343164026737213</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.02000000000000007</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0.5570606055516736</v>
@@ -74879,7 +74879,7 @@
         <v>0.3478979170322418</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.1199999999999999</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0.5570607439280583</v>
